--- a/outputs/tables/descriptive_statistics_all_variables.xlsx
+++ b/outputs/tables/descriptive_statistics_all_variables.xlsx
@@ -316,28 +316,28 @@
     <t xml:space="preserve">All rows in source file</t>
   </si>
   <si>
-    <t xml:space="preserve">Consent criterion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consent == 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commitment criterion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not applied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attention-check criterion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ac_total &gt;= 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final analysis sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All active criteria</t>
+    <t xml:space="preserve">Core criteria passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consent, commitment, and attention criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attitude-scale eligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least 80% of attitude items valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competence-scale eligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least 80% of competence items valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligible for both scales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligible for both attitude and competence scores</t>
   </si>
 </sst>
 </file>
@@ -1330,19 +1330,19 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>1211</v>
+        <v>941</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.222956234516928</v>
       </c>
       <c r="E2" t="n">
-        <v>0.777043765483072</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.416401166113702</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1354,19 +1354,19 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>-1.32955916211913</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-0.232462348329883</v>
+      <c r="L2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1374,19 +1374,19 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>1211</v>
+        <v>1018</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.159372419488026</v>
       </c>
       <c r="E3" t="n">
-        <v>0.840627580511974</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.366174238251884</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1398,19 +1398,19 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>-1.85893089694553</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.45682912151063</v>
+      <c r="L3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1418,19 +1418,19 @@
         <v>45</v>
       </c>
       <c r="B4" t="n">
-        <v>1211</v>
+        <v>1043</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.138728323699422</v>
       </c>
       <c r="E4" t="n">
-        <v>0.861271676300578</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.345805613023788</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1442,19 +1442,19 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>-2.08772407168588</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.36054309570254</v>
+      <c r="L4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1462,19 +1462,19 @@
         <v>56</v>
       </c>
       <c r="B5" t="n">
-        <v>1211</v>
+        <v>987</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.184971098265896</v>
       </c>
       <c r="E5" t="n">
-        <v>0.815028901734104</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.388434529182873</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1486,19 +1486,19 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>-1.62070433297123</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.627202501146863</v>
+      <c r="L5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5881,7 +5881,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="48.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>

--- a/outputs/tables/descriptive_statistics_all_variables.xlsx
+++ b/outputs/tables/descriptive_statistics_all_variables.xlsx
@@ -11,13 +11,15 @@
     <sheet name="Categorical_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Scale_items" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Open_text_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sample_flow" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Attention_subsamples" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Model_missingness" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Score_availability" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -211,16 +213,70 @@
     <t xml:space="preserve">additional_comments</t>
   </si>
   <si>
-    <t xml:space="preserve">competence_ET_2_raw</t>
+    <t xml:space="preserve">source_row</t>
   </si>
   <si>
     <t xml:space="preserve">Other numeric</t>
   </si>
   <si>
-    <t xml:space="preserve">competence_US_3_raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_AW_8_raw</t>
+    <t xml:space="preserve">competence_AW_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_US_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ET_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_3_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_6_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_8_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_9_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_10_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_15_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_19_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_20_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_1_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_2_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_3_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_4_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_competence_recalculated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_att_recalculated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_total_recalculated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac_failed_recalculated</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
@@ -304,40 +360,115 @@
     <t xml:space="preserve">mean_characters</t>
   </si>
   <si>
-    <t xml:space="preserve">stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All rows in source file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core criteria passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consent, commitment, and attention criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attitude-scale eligible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At least 80% of attitude items valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competence-scale eligible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At least 80% of competence items valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eligible for both scales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eligible for both attitude and competence scores</t>
+    <t xml:space="preserve">sample_key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum_correct_attention_checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all_core</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All core-eligible observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fail_at_most_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed at most two attention checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fail_at_most_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed at most one attention check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pass_all_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed all four attention checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required_variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rows_in_core_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rows_complete_for_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rows_excluded_for_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attitude two-factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_1, att_pos_2, att_pos_4, att_pos_5, att_pos_7, att_pos_11, att_pos_12, att_pos_13, att_pos_14, att_pos_16, att_pos_17, att_pos_18, att_neg_3_r, att_neg_6_r, att_neg_8_r, att_neg_9_r, att_neg_10_r, att_neg_15_r, att_neg_19_r, att_neg_20_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No global drop_na(). Complete-case filtering is applied only to the variables required by this specific analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competence four-factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_AW_1, competence_AW_8_r, competence_AW_9, competence_US_1, competence_US_3_r, competence_US_5, competence_EV_2, competence_EV_3, competence_EV_6, competence_ET_1, competence_ET_2_r, competence_ET_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadrant: positive and negative attitudes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_positive, attitude_negative_concern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">core_sample_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unavailable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">available_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_negative_concern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_negative_favorable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_usage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_total</t>
   </si>
 </sst>
 </file>
@@ -384,9 +515,23 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:E9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:E9"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="score"/>
+    <tableColumn id="2" name="available"/>
+    <tableColumn id="3" name="core_sample_n"/>
+    <tableColumn id="4" name="unavailable"/>
+    <tableColumn id="5" name="available_pct"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:B61" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:B78" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B78"/>
   <tableColumns count="2">
     <tableColumn id="1" name="variable"/>
     <tableColumn id="2" name="type"/>
@@ -396,8 +541,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:N58" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:N58"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:N71" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:N71"/>
   <tableColumns count="14">
     <tableColumn id="1" name="variable"/>
     <tableColumn id="2" name="n"/>
@@ -466,12 +611,28 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:C6" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C6"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="stage"/>
-    <tableColumn id="2" name="rule"/>
-    <tableColumn id="3" name="n"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:D5" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D5"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="sample_key"/>
+    <tableColumn id="2" name="sample_label"/>
+    <tableColumn id="3" name="minimum_correct_attention_checks"/>
+    <tableColumn id="4" name="n"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:F4" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:F4"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="model"/>
+    <tableColumn id="2" name="required_variables"/>
+    <tableColumn id="3" name="rows_in_core_sample"/>
+    <tableColumn id="4" name="rows_complete_for_model"/>
+    <tableColumn id="5" name="rows_excluded_for_model"/>
+    <tableColumn id="6" name="decision"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -759,7 +920,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="26.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="21.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1248,6 +1409,142 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1265,7 +1562,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="26.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
@@ -1286,43 +1583,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="L1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="M1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="N1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -1547,7 +1844,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="B7" t="n">
         <v>1211</v>
@@ -1559,39 +1856,39 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.61767134599505</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.679074378036414</v>
+        <v>0.388434529182873</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.62070433297123</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.627202501146863</v>
+      </c>
+      <c r="N7" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-1.50655833137627</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.797788441478528</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" t="n">
         <v>1211</v>
@@ -1603,39 +1900,39 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3.29397192402973</v>
+        <v>1.61767134599505</v>
       </c>
       <c r="F8" t="n">
-        <v>1.23761500677562</v>
+        <v>0.679074378036414</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.50655833137627</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.797788441478528</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1.69943319195659</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.61490688820899</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="B9" t="n">
         <v>1211</v>
@@ -1647,39 +1944,39 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>27.3104872006606</v>
+        <v>0.777043765483072</v>
       </c>
       <c r="F9" t="n">
-        <v>11.5197012993785</v>
+        <v>0.416401166113702</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53653798086913</v>
+        <v>-1.32955916211913</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6321081901793</v>
+        <v>-0.232462348329883</v>
       </c>
       <c r="N9" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="B10" t="n">
         <v>1211</v>
@@ -1691,13 +1988,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7514450867052</v>
+        <v>2.40792733278282</v>
       </c>
       <c r="F10" t="n">
-        <v>0.947456347191404</v>
+        <v>0.705634874799491</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -1706,24 +2003,24 @@
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.606307517722082</v>
+        <v>1.42070137834941</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.502791680680144</v>
+        <v>0.47253121174125</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
         <v>1211</v>
@@ -1735,13 +2032,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.30222956234517</v>
+        <v>3.29397192402973</v>
       </c>
       <c r="F11" t="n">
-        <v>0.961826765807059</v>
+        <v>1.23761500677562</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -1750,16 +2047,16 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.020754825507454</v>
+        <v>-1.69943319195659</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.281532137493195</v>
+        <v>1.61490688820899</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -1767,7 +2064,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B12" t="n">
         <v>1211</v>
@@ -1779,39 +2076,39 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3.12386457473163</v>
+        <v>1.59207266721718</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14899176564178</v>
+        <v>0.705634874799491</v>
       </c>
       <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.42070137834941</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.472531211741248</v>
+      </c>
+      <c r="N12" t="n">
         <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.0957531331996792</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-0.733465430213717</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B13" t="n">
         <v>1211</v>
@@ -1823,39 +2120,39 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3.01403798513625</v>
+        <v>27.3104872006606</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0518623210086</v>
+        <v>11.5197012993785</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0534881630810305</v>
+        <v>1.53653798086913</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.508413324565225</v>
+        <v>1.6321081901793</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B14" t="n">
         <v>1211</v>
@@ -1867,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3.02725020644096</v>
+        <v>2.7514450867052</v>
       </c>
       <c r="F14" t="n">
-        <v>1.04371426031252</v>
+        <v>0.947456347191404</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -1879,27 +2176,27 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0935318701433715</v>
+        <v>-0.606307517722082</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.381319565223999</v>
+        <v>-0.502791680680144</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B15" t="n">
         <v>1211</v>
@@ -1911,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3.29397192402973</v>
+        <v>3.30222956234517</v>
       </c>
       <c r="F15" t="n">
-        <v>0.911517667802013</v>
+        <v>0.961826765807059</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -1932,10 +2229,10 @@
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.160711064236988</v>
+        <v>-0.020754825507454</v>
       </c>
       <c r="M15" t="n">
-        <v>0.154304550600735</v>
+        <v>-0.281532137493195</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1943,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B16" t="n">
         <v>1211</v>
@@ -1955,20 +2252,20 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3.63088356729975</v>
+        <v>2.69777043765483</v>
       </c>
       <c r="F16" t="n">
-        <v>0.872918991528461</v>
+        <v>0.961826765807059</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
@@ -1976,10 +2273,10 @@
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.269541732552137</v>
+        <v>0.020754825507454</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0784732698128616</v>
+        <v>-0.281532137493195</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1987,7 +2284,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
         <v>1211</v>
@@ -1999,16 +2296,16 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3.64987613542527</v>
+        <v>3.12386457473163</v>
       </c>
       <c r="F17" t="n">
-        <v>0.937531258507121</v>
+        <v>1.14899176564178</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>4</v>
@@ -2020,10 +2317,10 @@
         <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.40774595149247</v>
+        <v>-0.0957531331996792</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0909641495555706</v>
+        <v>-0.733465430213717</v>
       </c>
       <c r="N17" t="n">
         <v>5</v>
@@ -2031,7 +2328,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B18" t="n">
         <v>1211</v>
@@ -2043,19 +2340,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>3.94302229562345</v>
+        <v>2.87613542526837</v>
       </c>
       <c r="F18" t="n">
-        <v>0.887502083991509</v>
+        <v>1.14899176564178</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2064,10 +2361,10 @@
         <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.916502988685632</v>
+        <v>0.0957531331996792</v>
       </c>
       <c r="M18" t="n">
-        <v>1.00044897356381</v>
+        <v>-0.733465430213717</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
@@ -2075,7 +2372,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B19" t="n">
         <v>1211</v>
@@ -2087,19 +2384,19 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2.43435177539224</v>
+        <v>3.01403798513625</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14398569825182</v>
+        <v>1.0518623210086</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2108,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.470667207307904</v>
+        <v>-0.0534881630810305</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.642431228633667</v>
+        <v>-0.508413324565225</v>
       </c>
       <c r="N19" t="n">
         <v>5</v>
@@ -2119,7 +2416,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B20" t="n">
         <v>1211</v>
@@ -2131,16 +2428,16 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3.56647398843931</v>
+        <v>2.98596201486375</v>
       </c>
       <c r="F20" t="n">
-        <v>0.845698324546656</v>
+        <v>1.0518623210086</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>4</v>
@@ -2152,10 +2449,10 @@
         <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.569046606316684</v>
+        <v>0.0534881630810305</v>
       </c>
       <c r="M20" t="n">
-        <v>0.52498036399026</v>
+        <v>-0.508413324565225</v>
       </c>
       <c r="N20" t="n">
         <v>5</v>
@@ -2163,7 +2460,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B21" t="n">
         <v>1211</v>
@@ -2175,16 +2472,16 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>3.55656482246078</v>
+        <v>3.02725020644096</v>
       </c>
       <c r="F21" t="n">
-        <v>0.908579542386996</v>
+        <v>1.04371426031252</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>4</v>
@@ -2196,10 +2493,10 @@
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.458652696569713</v>
+        <v>-0.0935318701433715</v>
       </c>
       <c r="M21" t="n">
-        <v>0.146556798773256</v>
+        <v>-0.381319565223999</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -2207,7 +2504,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B22" t="n">
         <v>1211</v>
@@ -2219,19 +2516,19 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4748142031379</v>
+        <v>2.97274979355904</v>
       </c>
       <c r="F22" t="n">
-        <v>1.08177304458766</v>
+        <v>1.04371426031252</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2240,10 +2537,10 @@
         <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.446422546647783</v>
+        <v>0.0935318701433715</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.397340861940949</v>
+        <v>-0.381319565223999</v>
       </c>
       <c r="N22" t="n">
         <v>5</v>
@@ -2251,7 +2548,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B23" t="n">
         <v>1211</v>
@@ -2263,16 +2560,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>3.94797687861272</v>
+        <v>3.29397192402973</v>
       </c>
       <c r="F23" t="n">
-        <v>0.746187302474419</v>
+        <v>0.911517667802013</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
@@ -2284,10 +2581,10 @@
         <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.941454245981439</v>
+        <v>-0.160711064236988</v>
       </c>
       <c r="M23" t="n">
-        <v>2.09136793088858</v>
+        <v>0.154304550600735</v>
       </c>
       <c r="N23" t="n">
         <v>5</v>
@@ -2295,7 +2592,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B24" t="n">
         <v>1211</v>
@@ -2307,20 +2604,20 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3.44921552436003</v>
+        <v>2.70602807597027</v>
       </c>
       <c r="F24" t="n">
-        <v>1.01867956776178</v>
+        <v>0.911517667802013</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
         <v>3</v>
       </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
@@ -2328,10 +2625,10 @@
         <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.584247251482457</v>
+        <v>0.160711064236988</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.136370059599742</v>
+        <v>0.154304550600735</v>
       </c>
       <c r="N24" t="n">
         <v>5</v>
@@ -2339,7 +2636,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B25" t="n">
         <v>1211</v>
@@ -2351,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3.50454170107349</v>
+        <v>3.63088356729975</v>
       </c>
       <c r="F25" t="n">
-        <v>0.942444956695127</v>
+        <v>0.872918991528461</v>
       </c>
       <c r="G25" t="n">
         <v>4</v>
@@ -2372,10 +2669,10 @@
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.557625395527172</v>
+        <v>-0.269541732552137</v>
       </c>
       <c r="M25" t="n">
-        <v>0.190227884464461</v>
+        <v>-0.0784732698128616</v>
       </c>
       <c r="N25" t="n">
         <v>5</v>
@@ -2383,7 +2680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B26" t="n">
         <v>1211</v>
@@ -2395,20 +2692,20 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>3.40214698596201</v>
+        <v>2.36911643270025</v>
       </c>
       <c r="F26" t="n">
-        <v>1.03138934534106</v>
+        <v>0.872918991528461</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="I26" t="n">
-        <v>4</v>
-      </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
@@ -2416,10 +2713,10 @@
         <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.509262954150447</v>
+        <v>0.269541732552137</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.21913612820242</v>
+        <v>-0.0784732698128616</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -2427,7 +2724,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B27" t="n">
         <v>1211</v>
@@ -2439,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>3.51692815854666</v>
+        <v>3.64987613542527</v>
       </c>
       <c r="F27" t="n">
-        <v>0.991035426787857</v>
+        <v>0.937531258507121</v>
       </c>
       <c r="G27" t="n">
         <v>4</v>
@@ -2460,10 +2757,10 @@
         <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.578790280341192</v>
+        <v>-0.40774595149247</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0876353482150978</v>
+        <v>-0.0909641495555706</v>
       </c>
       <c r="N27" t="n">
         <v>5</v>
@@ -2471,7 +2768,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B28" t="n">
         <v>1211</v>
@@ -2483,19 +2780,19 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3.03385631709331</v>
+        <v>2.35012386457473</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0283630139348</v>
+        <v>0.937531258507121</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -2504,10 +2801,10 @@
         <v>5</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.1541510272855</v>
+        <v>0.40774595149247</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.401189313125486</v>
+        <v>-0.0909641495555706</v>
       </c>
       <c r="N28" t="n">
         <v>5</v>
@@ -2515,7 +2812,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B29" t="n">
         <v>1211</v>
@@ -2527,10 +2824,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.17341040462428</v>
+        <v>3.94302229562345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.83694832084151</v>
+        <v>0.887502083991509</v>
       </c>
       <c r="G29" t="n">
         <v>4</v>
@@ -2548,10 +2845,10 @@
         <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.25534086465921</v>
+        <v>-0.916502988685632</v>
       </c>
       <c r="M29" t="n">
-        <v>2.23753897818405</v>
+        <v>1.00044897356381</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2559,7 +2856,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B30" t="n">
         <v>1211</v>
@@ -2571,19 +2868,19 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>3.35342691990091</v>
+        <v>2.05697770437655</v>
       </c>
       <c r="F30" t="n">
-        <v>1.00195399107614</v>
+        <v>0.887502083991509</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -2592,10 +2889,10 @@
         <v>5</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.395217981829148</v>
+        <v>0.916502988685632</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.255785677568379</v>
+        <v>1.00044897356381</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2603,7 +2900,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B31" t="n">
         <v>1211</v>
@@ -2615,39 +2912,39 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1.01073492981007</v>
+        <v>2.43435177539224</v>
       </c>
       <c r="F31" t="n">
-        <v>0.137451556943429</v>
+        <v>1.14398569825182</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
-        <v>3.89922511502129</v>
+        <v>0.470667207307904</v>
       </c>
       <c r="M31" t="n">
-        <v>48.9542747129757</v>
+        <v>-0.642431228633667</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B32" t="n">
         <v>1211</v>
@@ -2659,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>3.78943022295623</v>
+        <v>3.56647398843931</v>
       </c>
       <c r="F32" t="n">
-        <v>0.967788954374757</v>
+        <v>0.845698324546656</v>
       </c>
       <c r="G32" t="n">
         <v>4</v>
@@ -2680,10 +2977,10 @@
         <v>5</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.826973753510035</v>
+        <v>-0.569046606316684</v>
       </c>
       <c r="M32" t="n">
-        <v>0.477691083758207</v>
+        <v>0.52498036399026</v>
       </c>
       <c r="N32" t="n">
         <v>5</v>
@@ -2691,7 +2988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B33" t="n">
         <v>1211</v>
@@ -2703,19 +3000,19 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.12469033856317</v>
+        <v>3.55656482246078</v>
       </c>
       <c r="F33" t="n">
-        <v>1.07032541544132</v>
+        <v>0.908579542386996</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -2724,10 +3021,10 @@
         <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.858065798707298</v>
+        <v>-0.458652696569713</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0604002102610575</v>
+        <v>0.146556798773256</v>
       </c>
       <c r="N33" t="n">
         <v>5</v>
@@ -2735,7 +3032,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B34" t="n">
         <v>1211</v>
@@ -2747,20 +3044,20 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3.87530966143683</v>
+        <v>2.4748142031379</v>
       </c>
       <c r="F34" t="n">
-        <v>1.07032541544132</v>
+        <v>1.08177304458766</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
         <v>3</v>
       </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
@@ -2768,10 +3065,10 @@
         <v>5</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.858065798707298</v>
+        <v>0.446422546647783</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0604002102610575</v>
+        <v>-0.397340861940949</v>
       </c>
       <c r="N34" t="n">
         <v>5</v>
@@ -2779,7 +3076,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B35" t="n">
         <v>1211</v>
@@ -2791,16 +3088,16 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>3.68620974401321</v>
+        <v>3.94797687861272</v>
       </c>
       <c r="F35" t="n">
-        <v>0.918478666112242</v>
+        <v>0.746187302474419</v>
       </c>
       <c r="G35" t="n">
         <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
         <v>4</v>
@@ -2812,10 +3109,10 @@
         <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.773371089258368</v>
+        <v>-0.941454245981439</v>
       </c>
       <c r="M35" t="n">
-        <v>0.50693731209711</v>
+        <v>2.09136793088858</v>
       </c>
       <c r="N35" t="n">
         <v>5</v>
@@ -2823,7 +3120,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B36" t="n">
         <v>1211</v>
@@ -2835,19 +3132,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3.92733278282411</v>
+        <v>3.44921552436003</v>
       </c>
       <c r="F36" t="n">
-        <v>0.917959147116928</v>
+        <v>1.01867956776178</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -2856,10 +3153,10 @@
         <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.13080634356006</v>
+        <v>-0.584247251482457</v>
       </c>
       <c r="M36" t="n">
-        <v>1.63526395981219</v>
+        <v>-0.136370059599742</v>
       </c>
       <c r="N36" t="n">
         <v>5</v>
@@ -2867,7 +3164,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="B37" t="n">
         <v>1211</v>
@@ -2879,17 +3176,17 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.88934764657308</v>
+        <v>3.50454170107349</v>
       </c>
       <c r="F37" t="n">
-        <v>1.21055024188709</v>
+        <v>0.942444956695127</v>
       </c>
       <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" t="n">
         <v>4</v>
       </c>
@@ -2900,10 +3197,10 @@
         <v>5</v>
       </c>
       <c r="L37" t="n">
-        <v>0.00849878735609732</v>
+        <v>-0.557625395527172</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.989074290221033</v>
+        <v>0.190227884464461</v>
       </c>
       <c r="N37" t="n">
         <v>5</v>
@@ -2911,7 +3208,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B38" t="n">
         <v>1211</v>
@@ -2923,17 +3220,17 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3.11065235342692</v>
+        <v>3.40214698596201</v>
       </c>
       <c r="F38" t="n">
-        <v>1.21055024188709</v>
+        <v>1.03138934534106</v>
       </c>
       <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
         <v>3</v>
       </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
       <c r="I38" t="n">
         <v>4</v>
       </c>
@@ -2944,10 +3241,10 @@
         <v>5</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.00849878735609732</v>
+        <v>-0.509262954150447</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.989074290221033</v>
+        <v>-0.21913612820242</v>
       </c>
       <c r="N38" t="n">
         <v>5</v>
@@ -2955,7 +3252,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n">
         <v>1211</v>
@@ -2967,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>3.6672171758877</v>
+        <v>3.51692815854666</v>
       </c>
       <c r="F39" t="n">
-        <v>0.971021666048781</v>
+        <v>0.991035426787857</v>
       </c>
       <c r="G39" t="n">
         <v>4</v>
@@ -2988,10 +3285,10 @@
         <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.832804051973554</v>
+        <v>-0.578790280341192</v>
       </c>
       <c r="M39" t="n">
-        <v>0.560186422507892</v>
+        <v>0.0876353482150978</v>
       </c>
       <c r="N39" t="n">
         <v>5</v>
@@ -2999,7 +3296,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n">
         <v>1211</v>
@@ -3011,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3.73410404624277</v>
+        <v>3.03385631709331</v>
       </c>
       <c r="F40" t="n">
-        <v>0.910172766675915</v>
+        <v>1.0283630139348</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
@@ -3032,10 +3329,10 @@
         <v>5</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.851660985755643</v>
+        <v>-0.1541510272855</v>
       </c>
       <c r="M40" t="n">
-        <v>0.765779485168641</v>
+        <v>-0.401189313125486</v>
       </c>
       <c r="N40" t="n">
         <v>5</v>
@@ -3043,7 +3340,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n">
         <v>1211</v>
@@ -3055,19 +3352,19 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>3.81833195706028</v>
+        <v>4.17341040462428</v>
       </c>
       <c r="F41" t="n">
-        <v>0.881411823218939</v>
+        <v>0.83694832084151</v>
       </c>
       <c r="G41" t="n">
         <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -3076,10 +3373,10 @@
         <v>5</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.0568910754778</v>
+        <v>-1.25534086465921</v>
       </c>
       <c r="M41" t="n">
-        <v>1.61301798479985</v>
+        <v>2.23753897818405</v>
       </c>
       <c r="N41" t="n">
         <v>5</v>
@@ -3087,7 +3384,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B42" t="n">
         <v>1211</v>
@@ -3099,13 +3396,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3.72997522708505</v>
+        <v>3.35342691990091</v>
       </c>
       <c r="F42" t="n">
-        <v>0.906679483244332</v>
+        <v>1.00195399107614</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
         <v>3</v>
@@ -3120,10 +3417,10 @@
         <v>5</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.898909644091287</v>
+        <v>-0.395217981829148</v>
       </c>
       <c r="M42" t="n">
-        <v>0.803860596539899</v>
+        <v>-0.255785677568379</v>
       </c>
       <c r="N42" t="n">
         <v>5</v>
@@ -3131,7 +3428,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B43" t="n">
         <v>1211</v>
@@ -3143,39 +3440,39 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3.81255161023947</v>
+        <v>1.01073492981007</v>
       </c>
       <c r="F43" t="n">
-        <v>0.934397412896003</v>
+        <v>0.137451556943429</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.89922511502129</v>
+      </c>
+      <c r="M43" t="n">
+        <v>48.9542747129757</v>
+      </c>
+      <c r="N43" t="n">
         <v>3</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-1.00503621607543</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.09283516654479</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" t="n">
         <v>1211</v>
@@ -3187,19 +3484,19 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>2.58794384805946</v>
+        <v>3.78943022295623</v>
       </c>
       <c r="F44" t="n">
-        <v>1.10273288621132</v>
+        <v>0.967788954374757</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -3208,10 +3505,10 @@
         <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>0.388330468520108</v>
+        <v>-0.826973753510035</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.684436241375205</v>
+        <v>0.477691083758207</v>
       </c>
       <c r="N44" t="n">
         <v>5</v>
@@ -3231,20 +3528,20 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3.41205615194054</v>
+        <v>2.12469033856317</v>
       </c>
       <c r="F45" t="n">
-        <v>1.10273288621132</v>
+        <v>1.07032541544132</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
         <v>3</v>
       </c>
-      <c r="I45" t="n">
-        <v>4</v>
-      </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
@@ -3252,10 +3549,10 @@
         <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.388330468520108</v>
+        <v>0.858065798707298</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.684436241375205</v>
+        <v>0.0604002102610575</v>
       </c>
       <c r="N45" t="n">
         <v>5</v>
@@ -3263,7 +3560,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B46" t="n">
         <v>1211</v>
@@ -3275,16 +3572,16 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>3.90668868703551</v>
+        <v>3.87530966143683</v>
       </c>
       <c r="F46" t="n">
-        <v>0.995218245774841</v>
+        <v>1.07032541544132</v>
       </c>
       <c r="G46" t="n">
         <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
         <v>5</v>
@@ -3296,10 +3593,10 @@
         <v>5</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.1648781451589</v>
+        <v>-0.858065798707298</v>
       </c>
       <c r="M46" t="n">
-        <v>1.23508315470645</v>
+        <v>0.0604002102610575</v>
       </c>
       <c r="N46" t="n">
         <v>5</v>
@@ -3307,7 +3604,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B47" t="n">
         <v>1211</v>
@@ -3319,39 +3616,39 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>3.68620974401321</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.918478666112242</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="M47" t="e">
-        <v>#NUM!</v>
+        <v>5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.773371089258368</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.50693731209711</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B48" t="n">
         <v>1211</v>
@@ -3363,39 +3660,39 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>2.0280759702725</v>
+        <v>3.92733278282411</v>
       </c>
       <c r="F48" t="n">
-        <v>0.63704211688597</v>
+        <v>0.917959147116928</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.0235934749740986</v>
+        <v>-1.13080634356006</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.540607120201282</v>
+        <v>1.63526395981219</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="B49" t="n">
         <v>1211</v>
@@ -3407,39 +3704,39 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.34351775392238</v>
+        <v>2.88934764657308</v>
       </c>
       <c r="F49" t="n">
-        <v>0.516741710476031</v>
+        <v>1.21055024188709</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
-        <v>0.598112414517959</v>
+        <v>0.00849878735609732</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.509433165953297</v>
+        <v>-0.989074290221033</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B50" t="n">
         <v>1211</v>
@@ -3451,39 +3748,39 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.262592898431049</v>
+        <v>3.11065235342692</v>
       </c>
       <c r="F50" t="n">
-        <v>0.440224828264604</v>
+        <v>1.21055024188709</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L50" t="n">
-        <v>1.07768142158735</v>
+        <v>-0.00849878735609732</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.839293766907571</v>
+        <v>-0.989074290221033</v>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B51" t="n">
         <v>1211</v>
@@ -3495,39 +3792,39 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>643.711808422791</v>
+        <v>3.6672171758877</v>
       </c>
       <c r="F51" t="n">
-        <v>371.04003306001</v>
+        <v>0.971021666048781</v>
       </c>
       <c r="G51" t="n">
-        <v>640</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>325.5</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>970.5</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>1280</v>
+        <v>5</v>
       </c>
       <c r="L51" t="n">
-        <v>0.00103256576061997</v>
+        <v>-0.832804051973554</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.20783583194316</v>
+        <v>0.560186422507892</v>
       </c>
       <c r="N51" t="n">
-        <v>1211</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B52" t="n">
         <v>1211</v>
@@ -3539,10 +3836,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>3.61354252683732</v>
+        <v>3.73410404624277</v>
       </c>
       <c r="F52" t="n">
-        <v>0.844592866151266</v>
+        <v>0.910172766675915</v>
       </c>
       <c r="G52" t="n">
         <v>4</v>
@@ -3560,10 +3857,10 @@
         <v>5</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.70367925813543</v>
+        <v>-0.851660985755643</v>
       </c>
       <c r="M52" t="n">
-        <v>0.97570084853789</v>
+        <v>0.765779485168641</v>
       </c>
       <c r="N52" t="n">
         <v>5</v>
@@ -3571,7 +3868,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B53" t="n">
         <v>1211</v>
@@ -3583,39 +3880,39 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.772089182493807</v>
+        <v>3.81833195706028</v>
       </c>
       <c r="F53" t="n">
-        <v>0.419658080389981</v>
+        <v>0.881411823218939</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.29564764169588</v>
+        <v>-1.0568910754778</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.321560676649696</v>
+        <v>1.61301798479985</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B54" t="n">
         <v>1211</v>
@@ -3627,31 +3924,31 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1.21965317919075</v>
+        <v>3.72997522708505</v>
       </c>
       <c r="F54" t="n">
-        <v>1.07317873948781</v>
+        <v>0.906679483244332</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L54" t="n">
-        <v>1.22720004311304</v>
+        <v>-0.898909644091287</v>
       </c>
       <c r="M54" t="n">
-        <v>0.852203095073565</v>
+        <v>0.803860596539899</v>
       </c>
       <c r="N54" t="n">
         <v>5</v>
@@ -3659,7 +3956,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B55" t="n">
         <v>1211</v>
@@ -3671,39 +3968,39 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.890999174236168</v>
+        <v>3.81255161023947</v>
       </c>
       <c r="F55" t="n">
-        <v>0.311769000891161</v>
+        <v>0.934397412896003</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L55" t="n">
-        <v>-2.50619080244162</v>
+        <v>-1.00503621607543</v>
       </c>
       <c r="M55" t="n">
-        <v>4.28453239522466</v>
+        <v>1.09283516654479</v>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B56" t="n">
         <v>1211</v>
@@ -3715,39 +4012,39 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>3.37241948802642</v>
+        <v>2.58794384805946</v>
       </c>
       <c r="F56" t="n">
-        <v>2.55599098714446</v>
+        <v>1.10273288621132</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>0.404634274748399</v>
+        <v>0.388330468520108</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.16824281862915</v>
+        <v>-0.684436241375205</v>
       </c>
       <c r="N56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B57" t="n">
         <v>1211</v>
@@ -3759,77 +4056,649 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.21139554087531</v>
+        <v>3.41205615194054</v>
       </c>
       <c r="F57" t="n">
-        <v>0.408466939835744</v>
+        <v>1.10273288621132</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L57" t="n">
-        <v>1.41194359630027</v>
+        <v>-0.388330468520108</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.00641853596688069</v>
+        <v>-0.684436241375205</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.90668868703551</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.995218245774841</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1.1648781451589</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.23508315470645</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M59" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.0280759702725</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.63704211688597</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.0235934749740986</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-0.540607120201282</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.34351775392238</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.516741710476031</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.598112414517959</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-0.509433165953297</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.262592898431049</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.440224828264604</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.07768142158735</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-0.839293766907571</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>643.711808422791</v>
+      </c>
+      <c r="F63" t="n">
+        <v>371.04003306001</v>
+      </c>
+      <c r="G63" t="n">
+        <v>640</v>
+      </c>
+      <c r="H63" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>970.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.00103256576061997</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-1.20783583194316</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3.61354252683732</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.844592866151266</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.70367925813543</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.97570084853789</v>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.772089182493807</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.419658080389981</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-1.29564764169588</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-0.321560676649696</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.21965317919075</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.07317873948781</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.22720004311304</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.852203095073565</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.890999174236168</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.311769000891161</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-2.50619080244162</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4.28453239522466</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>607</v>
+      </c>
+      <c r="F68" t="n">
+        <v>349.729895776727</v>
+      </c>
+      <c r="G68" t="n">
+        <v>607</v>
+      </c>
+      <c r="H68" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>909.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-1.20297315622456</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.37241948802642</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.55599098714446</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.404634274748399</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-1.16824281862915</v>
+      </c>
+      <c r="N69" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.21139554087531</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.408466939835744</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.41194359630027</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-0.00641853596688069</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
         <v>20</v>
       </c>
-      <c r="B58" t="n">
-        <v>1211</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="B71" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
         <v>0.258464079273328</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F71" t="n">
         <v>0.437971227391349</v>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
         <v>1.10206540524029</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M71" t="n">
         <v>-0.786098929541944</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N71" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3858,13 +4727,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -4624,37 +5493,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="K1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
@@ -4662,7 +5531,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C2" t="n">
         <v>1211</v>
@@ -4697,7 +5566,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>1211</v>
@@ -4732,7 +5601,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C4" t="n">
         <v>1211</v>
@@ -4767,7 +5636,7 @@
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C5" t="n">
         <v>1211</v>
@@ -4802,7 +5671,7 @@
         <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C6" t="n">
         <v>1211</v>
@@ -4837,7 +5706,7 @@
         <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
         <v>1211</v>
@@ -4872,7 +5741,7 @@
         <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
         <v>1211</v>
@@ -4907,7 +5776,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
         <v>1211</v>
@@ -4942,7 +5811,7 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
         <v>1211</v>
@@ -4977,7 +5846,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C11" t="n">
         <v>1211</v>
@@ -5012,7 +5881,7 @@
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C12" t="n">
         <v>1211</v>
@@ -5047,7 +5916,7 @@
         <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C13" t="n">
         <v>1211</v>
@@ -5082,7 +5951,7 @@
         <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C14" t="n">
         <v>1211</v>
@@ -5117,7 +5986,7 @@
         <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C15" t="n">
         <v>1211</v>
@@ -5152,7 +6021,7 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C16" t="n">
         <v>1211</v>
@@ -5187,7 +6056,7 @@
         <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C17" t="n">
         <v>1211</v>
@@ -5222,7 +6091,7 @@
         <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C18" t="n">
         <v>1211</v>
@@ -5257,7 +6126,7 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C19" t="n">
         <v>1211</v>
@@ -5292,7 +6161,7 @@
         <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C20" t="n">
         <v>1211</v>
@@ -5327,7 +6196,7 @@
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C21" t="n">
         <v>1211</v>
@@ -5362,7 +6231,7 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C22" t="n">
         <v>1211</v>
@@ -5397,7 +6266,7 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C23" t="n">
         <v>1211</v>
@@ -5406,13 +6275,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.12469033856317</v>
+        <v>3.87530966143683</v>
       </c>
       <c r="F23" t="n">
         <v>1.07032541544132</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -5421,7 +6290,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.858065798707298</v>
+        <v>-0.858065798707298</v>
       </c>
       <c r="K23" t="n">
         <v>0.0604002102610575</v>
@@ -5432,7 +6301,7 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C24" t="n">
         <v>1211</v>
@@ -5467,7 +6336,7 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C25" t="n">
         <v>1211</v>
@@ -5502,7 +6371,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C26" t="n">
         <v>1211</v>
@@ -5511,13 +6380,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2.58794384805946</v>
+        <v>3.41205615194054</v>
       </c>
       <c r="F26" t="n">
         <v>1.10273288621132</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -5526,7 +6395,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>0.388330468520108</v>
+        <v>-0.388330468520108</v>
       </c>
       <c r="K26" t="n">
         <v>-0.684436241375205</v>
@@ -5537,7 +6406,7 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C27" t="n">
         <v>1211</v>
@@ -5572,7 +6441,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C28" t="n">
         <v>1211</v>
@@ -5607,7 +6476,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C29" t="n">
         <v>1211</v>
@@ -5642,7 +6511,7 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C30" t="n">
         <v>1211</v>
@@ -5677,7 +6546,7 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C31" t="n">
         <v>1211</v>
@@ -5712,7 +6581,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C32" t="n">
         <v>1211</v>
@@ -5721,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2.88934764657308</v>
+        <v>3.11065235342692</v>
       </c>
       <c r="F32" t="n">
         <v>1.21055024188709</v>
@@ -5736,7 +6605,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>0.00849878735609732</v>
+        <v>-0.00849878735609732</v>
       </c>
       <c r="K32" t="n">
         <v>-0.989074290221033</v>
@@ -5747,7 +6616,7 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C33" t="n">
         <v>1211</v>
@@ -5803,16 +6672,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
@@ -5880,75 +6749,80 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="48.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="35.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="4.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>115</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>1211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C3" t="n">
-        <v>1211</v>
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>872</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C4" t="n">
-        <v>1211</v>
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1211</v>
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5958,4 +6832,280 @@
     <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="245.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="113.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId9"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="13.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId10"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/outputs/tables/descriptive_statistics_all_variables.xlsx
+++ b/outputs/tables/descriptive_statistics_all_variables.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -369,28 +369,43 @@
     <t xml:space="preserve">minimum_correct_attention_checks</t>
   </si>
   <si>
+    <t xml:space="preserve">sample_role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attention_key_status</t>
+  </si>
+  <si>
     <t xml:space="preserve">all_core</t>
   </si>
   <si>
     <t xml:space="preserve">All core-eligible observations</t>
   </si>
   <si>
+    <t xml:space="preserve">Primary analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated against observed response coding</t>
+  </si>
+  <si>
     <t xml:space="preserve">fail_at_most_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Failed at most two attention checks</t>
+    <t xml:space="preserve">At least two checks correct (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity analysis; key not yet validated</t>
   </si>
   <si>
     <t xml:space="preserve">fail_at_most_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Failed at most one attention check</t>
+    <t xml:space="preserve">At least three checks correct (provisional)</t>
   </si>
   <si>
     <t xml:space="preserve">pass_all_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Passed all four attention checks</t>
+    <t xml:space="preserve">All four checks correct (provisional)</t>
   </si>
   <si>
     <t xml:space="preserve">model</t>
@@ -611,13 +626,15 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:D5" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D5"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:F5" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:F5"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="sample_key"/>
     <tableColumn id="2" name="sample_label"/>
     <tableColumn id="3" name="minimum_correct_attention_checks"/>
-    <tableColumn id="4" name="n"/>
+    <tableColumn id="4" name="sample_role"/>
+    <tableColumn id="5" name="attention_key_status"/>
+    <tableColumn id="6" name="n"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1856,34 +1873,34 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.815028901734104</v>
+        <v>1.67630057803468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.388434529182873</v>
+        <v>0.654993424097705</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.62070433297123</v>
+        <v>-1.78909452195644</v>
       </c>
       <c r="M7" t="n">
-        <v>0.627202501146863</v>
+        <v>1.67515602756819</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1944,34 +1961,34 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.777043765483072</v>
+        <v>1.61767134599505</v>
       </c>
       <c r="F9" t="n">
-        <v>0.416401166113702</v>
+        <v>0.679074378036414</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.32955916211913</v>
+        <v>-1.50655833137627</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.232462348329883</v>
+        <v>0.797788441478528</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1988,34 +2005,34 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.40792733278282</v>
+        <v>0.706028075970273</v>
       </c>
       <c r="F10" t="n">
-        <v>0.705634874799491</v>
+        <v>1.23761500677562</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42070137834941</v>
+        <v>1.69943319195659</v>
       </c>
       <c r="M10" t="n">
-        <v>0.47253121174125</v>
+        <v>1.61490688820899</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2076,34 +2093,34 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.59207266721718</v>
+        <v>3.29397192402973</v>
       </c>
       <c r="F12" t="n">
-        <v>0.705634874799491</v>
+        <v>1.23761500677562</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.42070137834941</v>
+        <v>-1.69943319195659</v>
       </c>
       <c r="M12" t="n">
-        <v>0.472531211741248</v>
+        <v>1.61490688820899</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -6750,9 +6767,11 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="35.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="43.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="4.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="43.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="42.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="4.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6766,63 +6785,93 @@
         <v>115</v>
       </c>
       <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" t="n">
         <v>1211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>872</v>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1073</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
+      <c r="D4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
+      <c r="D5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" t="n">
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -6849,30 +6898,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
         <v>1211</v>
@@ -6884,15 +6933,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
         <v>1211</v>
@@ -6904,15 +6953,15 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C4" t="n">
         <v>1211</v>
@@ -6924,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -6950,24 +6999,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B2" t="n">
         <v>1211</v>
@@ -6984,7 +7033,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B3" t="n">
         <v>1211</v>
@@ -7001,7 +7050,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B4" t="n">
         <v>1211</v>
@@ -7018,7 +7067,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B5" t="n">
         <v>1211</v>
@@ -7035,7 +7084,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B6" t="n">
         <v>1211</v>
@@ -7052,7 +7101,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B7" t="n">
         <v>1211</v>
@@ -7069,7 +7118,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B8" t="n">
         <v>1211</v>
@@ -7086,7 +7135,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B9" t="n">
         <v>1211</v>
